--- a/Översikt NÄSSJÖ.xlsx
+++ b/Översikt NÄSSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46041</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45131</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46168</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45460</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45919</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45680</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>45881</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45411</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>45804</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>45394</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45692</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45029</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>46258</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45393</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>45419</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45810</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>44537</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>45590</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>45419</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>44819</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>45527</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44928</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44928</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45096</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45841</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>44586</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>44848</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>45645</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>45943</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>46140</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>45610</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>46049</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>46048</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>44886</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45530</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>46104</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>46107</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>46129</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>45899</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>46258</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>46283</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45841</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45841</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>45108</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45113</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45013</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45051</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>45712</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44463</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44459</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44546</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44529</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>44503</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44585</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>44838</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44588</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44483</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44573</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44827</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44691</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>44579</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44603</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44502</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44818</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>44586</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44463</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44508</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>44613</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>44727</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>44541</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>44844</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>44477</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>44837</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44460</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44466</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>44519</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>44659</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>44701</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>44579</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>44474</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>44721</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>44670</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>44524</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>44487</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>44750</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>44678</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>44858</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44887</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44635</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>44811</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>44568</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>44650</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>45009</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>45481</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>45369</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45454</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>44988</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>45021</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45670</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45754</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>45213</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>45704</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>45720</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>44972</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45219</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45302</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>45238</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45154</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>44867</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>45277</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>45166</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>45380</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45275</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45238</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>45162</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>45503</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>45031</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45111</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44945</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45328</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>45637</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>45148</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45259</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45109</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45109</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>45335</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45335</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>45485</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>45013</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>45317</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45189</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45188</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>45604</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>45693</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>45460</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>45014</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>45303</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>45732</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>45517</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45181</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>45475</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44928</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>44484</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45677</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45182</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45211</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>45412</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45188</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45402</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45446</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>45041</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>44945</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>45154</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>44699</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45046</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45212</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45488</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45827</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>44928</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>44928</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45732</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45980</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>44904</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>44487</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>45742</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45841</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45322</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>45889</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45211</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>45800</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>45888</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>45679</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>45889</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45245</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45821</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45077</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>44939</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>45343</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>45887</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45890</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44609</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>45083</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45573</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44946</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45460</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44873</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45892</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>45916</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45671</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45370</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44594</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45757</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45083</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45358</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45899</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45215</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45365</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45365</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>46001</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>44946</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45904</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>45335</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44956</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45631</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>45904</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>45873</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45907</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45907</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45106</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45412</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45737</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45737</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44472</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>45776</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45733</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>46140</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45601</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45694</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45162</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45917</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44980</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45919</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45361</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44541</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44867</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44873</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>44776</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45328</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45277</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45742</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45448</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45398</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44826</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>44826</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>46146</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45702</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45212</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45942</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45943</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45943</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45363</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45008</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45391</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45391</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45944</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>45299</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>45118</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>44928</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>45279</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>45188</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45951</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>44804</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45625</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>45644</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45454</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45112</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>45187</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>44956</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>44858</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45460</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>45742</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45259</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>45209</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>45320</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>45372</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>45372</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22471,7 +22471,7 @@
         <v>45567</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>45343</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>45169</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>45566</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>45184</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>45975</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>45154</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45154</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45760</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>45009</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>45980</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>44664</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>46154</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>45630</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>45281</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>45091</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45610</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>45694</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44974</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>45720</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>45210</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45992</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>45838</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44858</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45270</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>46163</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45995</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45203</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45680</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>45995</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>45380</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>45999</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>46000</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>45103</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>46000</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45604</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45257</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>46000</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45302</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>45069</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>45693</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>46008</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>45168</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>44460</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45404</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45215</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>46170</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>46021</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45259</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>46030</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45069</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>46174</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45266</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>46174</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>44874</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>45614</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>45246</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>46174</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>44484</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>45148</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>46044</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>46174</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46044</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>46048</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>46048</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>44664</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>46049</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45210</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44902</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>46051</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>46055</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>46051</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>45198</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>46055</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>45590</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>45595</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>46055</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>46057</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>46059</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>45236</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>46059</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>45419</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>45756</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>46061</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>44813</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>44816</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45169</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>46070</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>46071</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>46071</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>46074</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45734</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>45372</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>45372</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>45372</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>46029</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>44460</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>46079</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45132</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>46029</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>44816</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>44972</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44994</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>45373</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>45394</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>46090</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>46187</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>46187</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44993</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>46187</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>45219</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>46091</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>46091</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>46190</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>46093</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>46093</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>46190</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>45695</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>46098</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>46098</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>45617</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>46196</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44564</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>44985</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>46100</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>46104</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>46196</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>46196</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>46101</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>45372</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>46101</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>45372</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>45617</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>45190</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44617</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>46105</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32474,7 +32474,7 @@
         <v>46198</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45163</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>46105</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>46198</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>46108</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>46198</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44974</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>46111</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>45109</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>46243</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>46243</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>46243</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>46243</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>45014</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33496,7 +33496,7 @@
         <v>44988</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>44904</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44894</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33715,7 +33715,7 @@
         <v>45695</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>46113</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33866,7 +33866,7 @@
         <v>45408</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45162</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44826</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34085,7 +34085,7 @@
         <v>46120</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>46120</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>46243</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>44608</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>46202</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>46127</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>44976</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>46129</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45213</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>45343</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>44881</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>46135</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>46135</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>45728</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>45377</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>46135</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>46135</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>44659</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>46020</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>46246</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>45692</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>45264</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45700</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44916</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>46204</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>44984</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>45579</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45187</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45308</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44992</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>45238</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>45275</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45181</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>46209</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>46209</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>45732</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>46209</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>46209</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>46209</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>46209</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>45275</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>45099</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>45056</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45616</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>44665</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>46212</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>44463</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44848</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>46254</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45309</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45113</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44874</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>45273</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>45204</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>46258</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>46258</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45734</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45163</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38354,7 +38354,7 @@
         <v>44603</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>45307</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>45316</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>44902</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38651,7 +38651,7 @@
         <v>44902</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38724,7 +38724,7 @@
         <v>46260</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38797,7 +38797,7 @@
         <v>45013</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45109</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45602</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>45685</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>45702</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>45702</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>45328</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39308,7 +39308,7 @@
         <v>44965</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39381,7 +39381,7 @@
         <v>45551</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39454,7 +39454,7 @@
         <v>45275</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>45277</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45611</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45776</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>46197</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>45615</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45784</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>45784</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45599</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>44605</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>45320</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45586</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>45791</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>45791</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>45791</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>45791</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>46283</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>46282</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>45795</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45260</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45795</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>46283</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>46283</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>45728</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>45742</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41279,7 +41279,7 @@
         <v>46260</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41352,7 +41352,7 @@
         <v>46283</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>45356</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>45733</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45723</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45729</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>45267</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45818</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45818</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45818</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45824</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>45821</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>45824</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45824</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>45824</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45794</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45841</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>45841</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>45843</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45843</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42739,7 +42739,7 @@
         <v>45843</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45747</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42885,7 +42885,7 @@
         <v>45791</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42958,7 +42958,7 @@
         <v>45719</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45721</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45732</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>45713</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>45881</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>45880</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45881</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>45880</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>45880</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>45109</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>45108</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45042</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45453</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>45411</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45029</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>45118</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>45082</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45112</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>44977</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>44482</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>45103</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>45100</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>45029</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>44613</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>45419</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>44575</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>45062</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44929,7 +44929,7 @@
         <v>45042</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>45809</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>45804</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>45835</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>46091</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>46091</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>46209</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45450,7 +45450,7 @@
         <v>46150</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>

--- a/Översikt NÄSSJÖ.xlsx
+++ b/Översikt NÄSSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46041</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45131</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46168</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45394</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45919</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45460</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>45680</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>45881</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45517</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45804</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45692</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45029</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45846</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45393</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>45419</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45810</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>44537</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>46021</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>45419</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44928</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>46048</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>46049</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44848</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>45527</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>46104</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>46107</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>45943</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45645</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>45899</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45530</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>45841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>46140</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44586</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>45841</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44819</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>46258</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>44886</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>46283</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>45590</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45610</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>45113</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45108</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>45013</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>45051</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45712</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>44613</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44594</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>44546</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>44529</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44503</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44585</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44838</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44588</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44483</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44827</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44573</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44691</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44579</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44603</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>44818</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>44508</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44613</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44727</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>44844</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44541</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>44477</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>44466</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44519</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44659</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>44701</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>44579</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44474</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44721</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44670</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44524</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44487</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44750</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44678</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>44858</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44887</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44635</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44811</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44650</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44568</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>45617</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44816</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45343</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44826</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45322</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44813</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45358</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45377</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45203</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45720</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45404</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45567</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45363</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45219</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>44874</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44848</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>44867</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45210</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44928</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>45394</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45460</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45454</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45109</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45365</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>45266</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>45517</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45307</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>45795</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>45795</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>46021</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>45154</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>45154</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>46030</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>45273</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>44946</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45260</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>45728</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>45742</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>45485</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>45723</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>45733</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44867</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>45356</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>45604</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>45729</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>45742</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>45827</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45800</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>45841</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>45679</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45890</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45246</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45888</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45889</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>45892</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>46044</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>45267</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>46044</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>46048</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>46048</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45899</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45904</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>46049</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45904</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>45873</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>46051</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45907</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>45907</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>46051</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>46055</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>46055</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>45737</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45737</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>46055</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>44994</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>44472</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45776</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>46057</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>46059</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>46059</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>46061</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>45917</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44902</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>45919</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>46070</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45014</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>46071</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>46071</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45031</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45419</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>44928</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>46074</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45212</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45212</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45369</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>46079</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45573</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>45372</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>44972</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>46029</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>46029</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>44617</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>46091</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>46091</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>45213</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>44945</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>46090</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>46093</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>46093</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45693</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>45181</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45209</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>44972</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45943</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45943</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>46098</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45942</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>46098</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44894</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>46101</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>46100</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45398</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>46101</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45944</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>46105</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>46105</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>44945</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>46104</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45112</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45951</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44939</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>46111</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>46108</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45317</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45041</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45009</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45013</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>46113</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44965</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>46120</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45204</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>46127</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>45818</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>46129</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>45637</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45975</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45980</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45014</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45631</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45702</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45702</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46135</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>46135</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>45671</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45728</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45630</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45887</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>46135</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>46135</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45154</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45992</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45995</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45889</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>44974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44974</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>44985</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45995</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>45733</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45694</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45999</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45198</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>44826</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45821</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45818</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45148</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>46000</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45818</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>44988</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>46001</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>46008</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45980</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>44804</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45277</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45824</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45677</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45824</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45732</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45694</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45821</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45824</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45824</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>45692</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45670</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45916</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>46140</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>45169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>46020</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45077</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45083</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45069</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45700</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45481</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>46146</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>44826</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45163</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45757</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45275</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45732</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44608</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>44858</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45794</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>46154</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>44928</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44928</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>45742</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45380</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45838</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>44664</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>45109</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>45732</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>45391</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45391</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45013</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45610</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45380</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45841</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>45841</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45843</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45843</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45843</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>46163</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44487</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45791</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>44665</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45747</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44992</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45408</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44484</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45277</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45719</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45721</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45163</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45335</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45335</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>46170</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46174</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>46174</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44993</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>44956</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45275</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>46174</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>46174</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45106</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>45373</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>44946</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45760</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45259</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45162</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45590</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45275</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45732</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45109</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45109</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45132</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44609</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45166</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45148</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>46187</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45211</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>46187</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>46187</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>45275</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>45579</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>45190</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29450,7 +29450,7 @@
         <v>45446</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>46190</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>46190</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>45742</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>45503</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>45118</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>45335</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>46196</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45111</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>46196</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>46196</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45713</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45880</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>45880</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>46198</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45880</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>46198</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>46198</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>46202</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45881</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>45881</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45210</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44594</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>45281</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>44988</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>46204</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>44816</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>45601</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>45162</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45372</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>45372</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>45372</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>44664</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45611</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>45103</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>46209</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32083,7 +32083,7 @@
         <v>46209</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>46209</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>46209</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>46209</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>46209</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45695</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45168</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>45685</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45083</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>46258</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>45702</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>46254</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46212</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45720</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>46258</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>46260</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>44776</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>45187</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>45188</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>45188</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>45460</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>45189</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>44699</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45695</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45259</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33933,7 +33933,7 @@
         <v>45169</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>45309</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>45734</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>45302</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>45245</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>45215</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         <v>45299</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>45219</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>45320</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45316</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>45361</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>46197</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         <v>45213</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>45734</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>45211</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44956</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44874</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>45259</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>45009</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45264</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45113</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>45328</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>45488</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>44904</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45279</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>46282</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>46283</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44984</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>46283</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>46243</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45308</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>45693</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>46243</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>46283</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>46243</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36498,7 +36498,7 @@
         <v>46243</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>46243</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44881</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36717,7 +36717,7 @@
         <v>45754</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>46283</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45551</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>46283</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45187</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>44902</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44603</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>46260</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44541</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>46287</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>46287</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45475</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>46290</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45402</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>46246</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45184</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>45091</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37963,7 +37963,7 @@
         <v>45162</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>45412</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>46289</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>46289</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>46000</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45343</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>45270</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45595</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45604</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>44916</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44873</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45372</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>45069</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38922,7 +38922,7 @@
         <v>45277</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44976</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>44980</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>44484</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>45154</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>45021</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45188</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39433,7 +39433,7 @@
         <v>45302</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>45372</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45372</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>45370</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>44902</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45412</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>45616</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>45182</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>45454</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44564</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45303</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>45460</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>45238</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45099</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40460,7 +40460,7 @@
         <v>44873</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>45614</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40606,7 +40606,7 @@
         <v>45602</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>45680</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>45617</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40825,7 +40825,7 @@
         <v>44659</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>45008</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>45566</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45046</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>45236</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45181</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>45056</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45704</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>45238</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>45257</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45343</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45448</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45756</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45365</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45644</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>45625</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45734</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42066,7 +42066,7 @@
         <v>45328</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>45328</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45238</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>45215</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>45776</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>45784</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45784</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42577,7 +42577,7 @@
         <v>45615</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45599</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44605</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42796,7 +42796,7 @@
         <v>45320</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
         <v>45791</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42942,7 +42942,7 @@
         <v>45791</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43015,7 +43015,7 @@
         <v>45586</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45791</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45791</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45108</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>45109</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44613</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43453,7 +43453,7 @@
         <v>44575</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43526,7 +43526,7 @@
         <v>45042</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>45453</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>45411</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>45029</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>45118</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45082</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>45112</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>44977</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>44482</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44183,7 +44183,7 @@
         <v>45103</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45100</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>45029</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>45419</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45062</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>45042</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45809</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45804</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>45835</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>46091</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44918,7 +44918,7 @@
         <v>46091</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>46209</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>46150</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>

--- a/Översikt NÄSSJÖ.xlsx
+++ b/Översikt NÄSSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46041</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45131</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46168</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45394</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45919</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45460</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>45680</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>45881</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45517</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45804</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45692</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45029</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45846</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45393</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>45419</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45810</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>44537</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>46021</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>45419</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44928</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>46048</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>46049</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44848</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>45527</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>46104</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>46107</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>45943</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45645</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>45899</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45530</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>45841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>46140</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44586</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>45841</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44819</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>46258</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>44886</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>46283</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>45590</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45610</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>45113</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45108</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>45013</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>45051</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45712</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>44613</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44594</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>44546</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>44529</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44503</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44585</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44838</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44588</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44483</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44827</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44573</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44691</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44579</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44603</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>44818</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>44508</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44613</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44727</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>44844</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44541</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>44477</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>44466</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44519</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44659</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>44701</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>44579</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44474</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44721</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44670</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44524</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44487</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44750</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44678</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>44858</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44887</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44635</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44811</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44650</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44568</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>45617</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44816</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45343</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44826</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45322</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44813</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45358</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45377</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45203</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45720</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45404</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45567</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45363</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45219</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>44874</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44848</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>44867</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45210</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44928</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>45394</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45460</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45454</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45109</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45365</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>45266</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>45517</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45307</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>45795</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>45795</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>46021</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>45154</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>45154</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>46030</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>45273</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>44946</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45260</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>45728</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>45742</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>45485</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>45723</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>45733</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44867</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>45356</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>45604</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>45729</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>45742</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>45827</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45800</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>45841</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>45679</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45890</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45246</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45888</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45889</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>45892</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>46044</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>45267</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>46044</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>46048</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>46048</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45899</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45904</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>46049</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45904</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>45873</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>46051</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45907</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>45907</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>46051</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>46055</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>46055</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>45737</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45737</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>46055</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>44994</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>44472</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45776</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>46057</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>46059</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>46059</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>46061</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>45917</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44902</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>45919</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>46070</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45014</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>46071</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>46071</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45031</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45419</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>44928</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>46074</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45212</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45212</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45369</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>46079</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45573</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>45372</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>44972</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>46029</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>46029</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>44617</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>46091</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>46091</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>45213</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>44945</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>46090</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>46093</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>46093</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45693</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>45181</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45209</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>44972</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45943</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45943</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>46098</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45942</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>46098</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44894</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>46101</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>46100</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45398</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>46101</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45944</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>46105</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>46105</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>44945</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>46104</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45112</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45951</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44939</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>46111</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>46108</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45317</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45041</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45009</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45013</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>46113</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44965</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>46120</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45204</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>46127</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>45818</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>46129</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>45637</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45975</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45980</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45014</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45631</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45702</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45702</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46135</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>46135</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>45671</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45728</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45630</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45887</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>46135</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>46135</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45154</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45992</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45995</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45889</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>44974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44974</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>44985</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45995</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>45733</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45694</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45999</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45198</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>44826</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45821</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45818</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45148</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>46000</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45818</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>44988</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>46001</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>46008</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45980</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>44804</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45277</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45824</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45677</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45824</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45732</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45694</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45821</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45824</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45824</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>45692</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45670</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45916</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>46140</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>45169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>46020</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45077</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45083</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45069</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45700</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45481</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>46146</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>44826</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45163</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45757</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45275</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45732</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44608</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>44858</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45794</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>46154</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>44928</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44928</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>45742</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45380</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45838</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>44664</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>45109</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>45732</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>45391</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45391</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45013</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45610</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45380</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45841</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>45841</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45843</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45843</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45843</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>46163</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44487</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45791</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>44665</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45747</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44992</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45408</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44484</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45277</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45719</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45721</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45163</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45335</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45335</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>46170</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46174</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>46174</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44993</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>44956</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45275</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>46174</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>46174</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45106</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>45373</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>44946</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45760</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45259</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45162</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45590</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45275</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45732</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45109</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45109</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45132</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44609</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45166</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45148</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>46187</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45211</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>46187</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>46187</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>45275</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>45579</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>45190</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29450,7 +29450,7 @@
         <v>45446</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>46190</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>46190</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>45742</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>45503</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>45118</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>45335</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>46196</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45111</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>46196</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>46196</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45713</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45880</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>45880</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>46198</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45880</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>46198</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>46198</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>46202</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45881</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>45881</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45210</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44594</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>45281</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>44988</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>46204</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>44816</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>45601</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>45162</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45372</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>45372</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>45372</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>44664</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45611</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>45103</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>46209</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32083,7 +32083,7 @@
         <v>46209</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>46209</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>46209</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>46209</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>46209</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45695</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45168</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>45685</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45083</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>46258</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>45702</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>46254</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46212</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45720</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>46258</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>46260</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>44776</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>45187</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>45188</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>45188</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>45460</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>45189</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>44699</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45695</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45259</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33933,7 +33933,7 @@
         <v>45169</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>45309</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>45734</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>45302</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>45245</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>45215</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         <v>45299</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>45219</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>45320</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45316</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>45361</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>46197</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         <v>45213</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>45734</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>45211</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44956</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44874</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>45259</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>45009</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45264</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45113</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>45328</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>45488</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>44904</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45279</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>46282</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>46283</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44984</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>46283</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>46243</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45308</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>45693</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>46243</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>46283</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>46243</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36498,7 +36498,7 @@
         <v>46243</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>46243</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44881</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36717,7 +36717,7 @@
         <v>45754</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>46283</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45551</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>46283</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45187</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>44902</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44603</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>46260</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44541</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>46287</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>46287</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45475</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>46290</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45402</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>46246</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45184</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>45091</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37963,7 +37963,7 @@
         <v>45162</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>45412</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>46289</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>46289</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>46000</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45343</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>45270</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45595</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45604</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>44916</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44873</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45372</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>45069</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38922,7 +38922,7 @@
         <v>45277</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44976</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>44980</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>44484</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>45154</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>45021</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45188</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39433,7 +39433,7 @@
         <v>45302</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>45372</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45372</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>45370</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>44902</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45412</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>45616</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>45182</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>45454</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44564</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45303</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>45460</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>45238</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45099</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40460,7 +40460,7 @@
         <v>44873</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>45614</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40606,7 +40606,7 @@
         <v>45602</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>45680</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>45617</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40825,7 +40825,7 @@
         <v>44659</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>45008</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>45566</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45046</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>45236</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45181</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>45056</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45704</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>45238</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>45257</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45343</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45448</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45756</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45365</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45644</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>45625</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45734</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42066,7 +42066,7 @@
         <v>45328</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>45328</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45238</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>45215</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>45776</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>45784</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45784</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42577,7 +42577,7 @@
         <v>45615</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45599</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44605</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42796,7 +42796,7 @@
         <v>45320</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
         <v>45791</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42942,7 +42942,7 @@
         <v>45791</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43015,7 +43015,7 @@
         <v>45586</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45791</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45791</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45108</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>45109</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>44613</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43453,7 +43453,7 @@
         <v>44575</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43526,7 +43526,7 @@
         <v>45042</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>45453</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>45411</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>45029</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>45118</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45082</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>45112</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>44977</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>44482</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44183,7 +44183,7 @@
         <v>45103</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45100</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>45029</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>45419</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45062</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>45042</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45809</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45804</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>45835</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>46091</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44918,7 +44918,7 @@
         <v>46091</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>46209</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>46150</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>

--- a/Översikt NÄSSJÖ.xlsx
+++ b/Översikt NÄSSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46041</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45131</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46168</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45460</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45919</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45881</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45394</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>45517</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45680</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45804</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45692</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45029</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45846</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45393</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>45419</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45810</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>44537</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>45590</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45419</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>46021</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>46049</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>46048</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>44819</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45527</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>44928</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>45943</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>44928</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45096</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>46104</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>46107</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45899</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>45841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>45841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44586</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45841</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>44848</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>45645</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46140</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>46258</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44886</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45530</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>46283</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>45108</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45113</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>45013</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>45051</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45712</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>44613</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44594</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>44503</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>44546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44529</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44585</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44838</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44588</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44483</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44827</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44573</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44691</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44579</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44603</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>44818</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>44508</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44613</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44727</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>44541</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44844</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>44477</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>44519</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44659</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44701</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>44579</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>44474</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44721</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44670</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44524</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44487</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44678</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44750</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44858</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>44887</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44568</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44811</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44650</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>45369</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>45454</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44988</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45481</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45213</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45021</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45670</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45754</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45720</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45219</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45154</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45277</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45166</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>45238</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44972</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45599</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44605</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>45704</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45302</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45031</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>45111</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>44867</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>45162</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>45380</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>45275</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>45238</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>45320</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>45827</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>46008</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>45503</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>45586</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>45328</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>44945</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>45637</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>45800</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45888</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>46021</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>45679</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>45889</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45890</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>45148</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>45259</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>46030</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>45899</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>45791</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>45791</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45904</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>45904</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>45873</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>45791</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>45109</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>45109</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>45907</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>45907</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>45791</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>45737</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45737</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>44472</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45776</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45335</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>45335</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>45795</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45260</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>46044</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45795</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>45189</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>45188</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>46044</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>45485</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>46048</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>46048</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>45013</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45728</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45742</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45317</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45604</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>46049</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45356</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>45917</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45733</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45723</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45729</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45267</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45211</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>46051</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>46055</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>46051</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>46055</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>45693</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45303</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>46055</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>45732</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>46057</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45014</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45460</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>46059</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45734</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>46059</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>46061</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45517</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>44928</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45181</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>46070</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>45475</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45942</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>45943</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45943</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>46071</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>46071</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>44484</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>46074</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>45182</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45412</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>45944</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45677</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>45188</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>46029</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>46079</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>46029</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45402</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>46090</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45446</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45041</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44945</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45154</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>46091</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>46091</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>46093</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45046</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>46093</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>44699</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>46098</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>46098</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>46100</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>45975</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>46104</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>46101</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45212</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>46101</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45818</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>46105</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>45818</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>46105</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>45980</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>46108</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>45818</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>46111</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45488</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>46113</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>45824</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>45821</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45824</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45824</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45824</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>46120</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44928</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>44928</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45732</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>45992</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>44904</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>44487</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>45995</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45322</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>45995</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>46127</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>46129</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>45999</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>46000</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>46135</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>46135</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>45211</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>45728</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>45245</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45077</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>44939</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45794</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45343</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>46135</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>46135</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>44609</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45083</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>45573</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>46020</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>44946</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45460</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44873</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45370</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>44594</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45841</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45692</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45757</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>45083</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45358</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45841</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45215</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>45365</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45365</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45843</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>44946</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45335</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45980</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>44956</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45631</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45843</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45843</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45106</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45412</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45747</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45791</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45889</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45601</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>45162</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>45821</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44980</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>45887</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45361</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>44541</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>45916</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>45671</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>44867</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44873</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>46001</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45719</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>44776</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45721</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45328</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>45277</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45742</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45448</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45398</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>45733</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>46140</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44826</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44826</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45702</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>45694</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45212</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45363</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45008</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45391</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45391</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>45299</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45118</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>44928</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45279</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45188</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>46146</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>44804</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45625</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45644</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45454</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45732</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45112</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45187</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>44956</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>44858</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>45460</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>45742</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28262,7 +28262,7 @@
         <v>45259</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>45209</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>45320</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>46154</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>45372</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28627,7 +28627,7 @@
         <v>45372</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>45567</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>45343</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>45169</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>45838</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45566</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>45184</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>45154</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>45154</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>46163</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45009</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45713</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44664</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>45630</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45281</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45091</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45881</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45880</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45881</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45610</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>46170</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45880</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>45694</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>46174</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45880</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>46174</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>44974</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>45720</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>46174</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>45210</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>46174</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>45742</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45841</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44858</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>45270</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31207,7 +31207,7 @@
         <v>45203</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>45680</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>45380</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>45103</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31499,7 +31499,7 @@
         <v>45604</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>46187</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>46187</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>45257</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45302</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>46187</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>45069</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>46190</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32083,7 +32083,7 @@
         <v>46190</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>45693</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>45168</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>46196</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>46196</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32448,7 +32448,7 @@
         <v>46196</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32521,7 +32521,7 @@
         <v>46198</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>46198</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>46198</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>45404</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>45215</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45259</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>46202</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>46204</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45069</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>45266</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44874</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>45614</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>46209</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>46209</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>45246</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>46209</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>46209</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>46209</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>46209</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>46212</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44484</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>45148</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>46258</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>46258</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>44664</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         <v>45210</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44902</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>45198</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45590</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>45595</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>46260</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45236</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>45419</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>45756</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>44813</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>44816</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>45169</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>45734</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45372</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45372</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45372</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>46197</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45132</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35690,7 +35690,7 @@
         <v>44816</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35763,7 +35763,7 @@
         <v>44972</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>44994</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35909,7 +35909,7 @@
         <v>45373</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35982,7 +35982,7 @@
         <v>45394</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>44993</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>46282</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>45219</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>45695</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>45617</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>44564</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44985</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>46283</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>45372</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>45372</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45617</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45190</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44617</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>46287</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>45163</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>46283</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>46243</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>46283</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37374,7 +37374,7 @@
         <v>46283</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>46260</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>46243</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>46243</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44974</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>46243</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>46243</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45109</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>46283</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>45014</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>44988</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>46246</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>44894</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45695</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45408</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45162</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>44826</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>44608</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>44976</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45213</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45343</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>46000</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>46289</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>46289</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>46290</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>44881</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>45377</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>46249</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>46294</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>46295</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>44659</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>46294</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>46294</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>46248</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46295</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>46295</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>46294</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>46295</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>45264</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40231,7 +40231,7 @@
         <v>45700</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>44916</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40377,7 +40377,7 @@
         <v>44984</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>45579</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>45187</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40596,7 +40596,7 @@
         <v>45308</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44992</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>46287</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>46254</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45238</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45275</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45181</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45732</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45275</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>45099</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45056</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>45616</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>44665</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44848</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45309</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>45113</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>44874</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45273</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>45204</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>45734</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45163</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>44603</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45307</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>45316</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>44902</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>44902</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45013</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42577,7 +42577,7 @@
         <v>45109</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45602</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>45685</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42796,7 +42796,7 @@
         <v>45702</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
         <v>45702</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42942,7 +42942,7 @@
         <v>45328</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43015,7 +43015,7 @@
         <v>44965</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45551</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45275</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45277</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>45611</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>45776</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43453,7 +43453,7 @@
         <v>45615</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43526,7 +43526,7 @@
         <v>45784</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>45784</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>45109</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>45108</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>45042</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45453</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>45411</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45029</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>45118</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44183,7 +44183,7 @@
         <v>45082</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45112</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>44977</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>44482</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45103</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>45100</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45029</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>44613</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44767,7 +44767,7 @@
         <v>45419</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>44575</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45062</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44986,7 +44986,7 @@
         <v>45042</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>45809</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45804</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>45835</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>46091</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>46091</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>46209</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45507,7 +45507,7 @@
         <v>46150</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>

--- a/Översikt NÄSSJÖ.xlsx
+++ b/Översikt NÄSSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46041</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45131</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46168</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45460</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45919</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45881</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45394</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>45517</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45680</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45804</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45692</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45029</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45846</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45393</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>45419</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45810</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>44537</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>45590</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45419</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>46021</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>46049</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>46048</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>44819</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45527</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>44928</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>45943</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>44928</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45096</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>46104</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>46107</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45899</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>45841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>45841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44586</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45841</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>44848</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>45645</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46140</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>46258</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44886</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45530</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>46283</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>45108</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45113</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>45013</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>45051</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45712</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>44613</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44594</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>44503</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>44546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44529</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44585</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44838</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44588</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44483</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44827</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44573</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44691</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44579</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44603</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>44818</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>44508</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44613</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44727</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>44541</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44844</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>44477</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>44519</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44659</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44701</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>44579</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>44474</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44721</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44670</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44524</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44487</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44678</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44750</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44858</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>44887</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44568</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44811</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44650</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>45369</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>45454</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44988</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45481</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45213</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45021</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45670</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45754</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45720</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45219</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45154</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45277</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45166</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>45238</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44972</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45599</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44605</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>45704</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45302</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45031</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>45111</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>44867</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>45162</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>45380</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>45275</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>45238</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>45320</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>45827</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>46008</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>45503</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>45586</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>45328</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>44945</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>45637</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>45800</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45888</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>46021</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>45679</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>45889</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45890</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>45148</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>45259</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>46030</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>45899</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>45791</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>45791</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45904</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>45904</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>45873</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>45791</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>45109</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>45109</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>45907</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>45907</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>45791</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>45737</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45737</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>44472</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45776</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45335</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>45335</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>45795</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45260</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>46044</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45795</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>45189</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>45188</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>46044</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>45485</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>46048</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>46048</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>45013</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45728</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45742</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45317</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45604</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>46049</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45356</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>45917</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45733</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45723</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45729</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45267</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45211</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>46051</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>46055</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>46051</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>46055</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>45693</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45303</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>46055</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>45732</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>46057</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45014</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45460</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>46059</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45734</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>46059</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>46061</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45517</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>44928</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45181</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>46070</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>45475</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45942</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>45943</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45943</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>46071</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>46071</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>44484</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>46074</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>45182</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45412</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>45944</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45677</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>45188</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>46029</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>46079</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>46029</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45402</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>46090</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45446</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45041</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44945</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45154</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>46091</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>46091</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>46093</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45046</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>46093</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>44699</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>46098</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>46098</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>46100</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>45975</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>46104</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>46101</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45212</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>46101</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45818</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>46105</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>45818</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>46105</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>45980</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>46108</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>45818</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>46111</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45488</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>46113</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>45824</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>45821</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45824</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45824</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45824</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>46120</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44928</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>44928</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45732</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>45992</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>44904</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>44487</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>45995</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45322</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>45995</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>46127</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>46129</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>45999</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>46000</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>46135</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>46135</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>45211</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>45728</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>45245</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45077</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>44939</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45794</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45343</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>46135</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>46135</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>44609</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45083</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>45573</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>46020</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>44946</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45460</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44873</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45370</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>44594</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45841</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45692</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45757</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>45083</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45358</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45841</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45215</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>45365</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45365</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45843</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>44946</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45335</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45980</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>44956</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45631</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45843</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45843</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45106</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45412</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45747</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45791</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45889</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45601</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>45162</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>45821</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44980</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>45887</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45361</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>44541</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>45916</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>45671</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>44867</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44873</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>46001</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45719</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>44776</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45721</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45328</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>45277</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45742</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45448</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45398</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>45733</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>46140</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44826</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44826</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45702</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>45694</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45212</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45363</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45008</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45391</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45391</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>45299</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45118</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>44928</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45279</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45188</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>46146</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>44804</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45625</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45644</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45454</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45732</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45112</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45187</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>44956</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>44858</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>45460</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>45742</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28262,7 +28262,7 @@
         <v>45259</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>45209</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>45320</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>46154</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>45372</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28627,7 +28627,7 @@
         <v>45372</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>45567</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>45343</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>45169</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>45838</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45566</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>45184</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>45154</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>45154</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>46163</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45009</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45713</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44664</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>45630</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45281</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45091</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45881</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45880</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45881</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45610</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>46170</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45880</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>45694</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>46174</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45880</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>46174</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>44974</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>45720</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>46174</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>45210</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>46174</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>45742</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45841</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44858</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>45270</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31207,7 +31207,7 @@
         <v>45203</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>45680</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>45380</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>45103</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31499,7 +31499,7 @@
         <v>45604</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>46187</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>46187</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>45257</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45302</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>46187</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>45069</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>46190</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32083,7 +32083,7 @@
         <v>46190</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>45693</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>45168</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>46196</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>46196</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32448,7 +32448,7 @@
         <v>46196</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32521,7 +32521,7 @@
         <v>46198</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>46198</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>46198</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>45404</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>45215</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45259</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>46202</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>46204</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45069</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>45266</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44874</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>45614</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>46209</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>46209</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>45246</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>46209</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>46209</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>46209</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>46209</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>46212</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44484</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>45148</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>46258</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>46258</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>44664</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         <v>45210</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44902</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>45198</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45590</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>45595</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>46260</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45236</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>45419</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>45756</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>44813</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>44816</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>45169</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>45734</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45372</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45372</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45372</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>46197</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45132</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35690,7 +35690,7 @@
         <v>44816</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35763,7 +35763,7 @@
         <v>44972</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>44994</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35909,7 +35909,7 @@
         <v>45373</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35982,7 +35982,7 @@
         <v>45394</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>44993</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>46282</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>45219</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>45695</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>45617</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>44564</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44985</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>46283</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>45372</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>45372</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45617</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45190</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44617</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>46287</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>45163</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>46283</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>46243</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>46283</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37374,7 +37374,7 @@
         <v>46283</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>46260</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>46243</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>46243</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44974</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>46243</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>46243</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45109</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>46283</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>45014</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>44988</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>46246</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>44894</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45695</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45408</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45162</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>44826</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>44608</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>44976</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45213</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45343</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>46000</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>46289</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>46289</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>46290</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>44881</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>45377</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>46249</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>46294</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>46295</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>44659</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>46294</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>46294</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>46248</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46295</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>46295</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>46294</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>46295</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>45264</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40231,7 +40231,7 @@
         <v>45700</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>44916</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40377,7 +40377,7 @@
         <v>44984</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>45579</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>45187</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40596,7 +40596,7 @@
         <v>45308</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44992</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>46287</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>46254</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45238</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45275</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45181</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45732</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45275</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>45099</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45056</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>45616</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>44665</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44848</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45309</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>45113</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>44874</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45273</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>45204</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>45734</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45163</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>44603</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45307</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>45316</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>44902</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>44902</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45013</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42577,7 +42577,7 @@
         <v>45109</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45602</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>45685</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42796,7 +42796,7 @@
         <v>45702</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
         <v>45702</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42942,7 +42942,7 @@
         <v>45328</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43015,7 +43015,7 @@
         <v>44965</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45551</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45275</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45277</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>45611</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>45776</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43453,7 +43453,7 @@
         <v>45615</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43526,7 +43526,7 @@
         <v>45784</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>45784</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>45109</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>45108</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>45042</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45453</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>45411</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45029</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>45118</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44183,7 +44183,7 @@
         <v>45082</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45112</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>44977</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>44482</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45103</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>45100</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45029</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>44613</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44767,7 +44767,7 @@
         <v>45419</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>44575</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45062</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44986,7 +44986,7 @@
         <v>45042</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>45809</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45804</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>45835</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>46091</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>46091</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>46209</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45507,7 +45507,7 @@
         <v>46150</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>

--- a/Översikt NÄSSJÖ.xlsx
+++ b/Översikt NÄSSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46041</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45131</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46168</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45394</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45460</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45680</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45881</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>45919</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45517</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45804</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45692</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>46303</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45029</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>46258</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45393</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>45419</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45810</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>44537</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45096</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44819</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>45419</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44928</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45610</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>44848</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45527</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45943</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45645</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>45841</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45841</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44886</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>46104</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>46107</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>45590</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>45899</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>45841</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>46048</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>46049</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>46140</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>46283</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>46258</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45113</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45108</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>45013</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45051</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45712</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>44546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>44529</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>44503</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>44838</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>44588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44483</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>44827</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>44573</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>44691</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>44579</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>44603</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>44502</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>44818</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>44586</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>44508</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>44613</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>44844</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>44541</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>44837</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44670</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44519</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>44678</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>44750</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>44659</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>44701</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44524</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44579</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>44858</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>44887</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44811</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44650</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>44568</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>44487</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45363</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>45154</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>45021</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>44826</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>45188</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>45302</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>44816</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>45163</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>45757</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44874</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>45372</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>45372</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>45617</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>44848</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>45275</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>45732</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>44858</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44608</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>44858</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>44867</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45720</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>44928</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45370</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>45219</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>44902</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>45343</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>44928</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>44928</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44826</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44813</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45358</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45377</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>45203</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45412</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>45616</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45322</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>45182</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>45454</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>45380</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>45210</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>44564</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>44664</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>45394</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45460</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>45109</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>45732</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45391</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45391</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45303</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45013</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45610</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45380</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45460</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>45238</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45454</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45099</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45109</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>45567</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>44873</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>45614</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44487</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>45602</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45680</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45404</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>44665</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45617</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45365</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45266</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44992</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>44659</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>45517</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>45408</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>45307</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45008</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>45566</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>45046</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>45236</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45181</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45056</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44484</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>45277</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>45154</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45154</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>45742</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>45273</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>45704</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>45827</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>45800</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>45163</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>45841</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45679</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44946</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>45335</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>45335</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45238</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45890</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45485</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44993</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45257</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>44956</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45275</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45343</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44867</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45604</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45888</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45889</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45448</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45756</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45365</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>45899</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45644</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45625</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45734</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45246</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45106</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45328</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45328</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45238</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45904</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45904</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45873</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45907</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45907</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45373</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>44946</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45215</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45737</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45737</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45776</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45776</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45259</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45162</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45590</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45275</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45784</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45109</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45109</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45784</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45132</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>44609</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45166</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45148</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44994</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45615</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>45211</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45275</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45917</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45579</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45190</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45599</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44902</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>44605</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45446</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45742</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45014</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45503</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45118</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45320</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>45335</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45031</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45791</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45791</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45419</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44928</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45586</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45212</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45212</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45791</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45791</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45369</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45111</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45573</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45795</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>45795</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45372</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>44972</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44617</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45260</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45728</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45742</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45723</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45733</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45356</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45729</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45210</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45213</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>44945</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>44594</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45281</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45267</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>44988</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45693</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45181</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>44816</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45601</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45209</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>44972</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45162</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45372</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45372</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45372</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>44664</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>44894</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>45398</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45611</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45103</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>44945</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>45112</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45695</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>45168</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45943</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45943</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>44939</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45942</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>45944</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45317</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45041</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45818</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45009</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45685</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45013</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>45083</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45818</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45818</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44965</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>45702</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45824</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>45824</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45821</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45824</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>45824</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>45720</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45204</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>45951</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>44776</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>45187</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>45188</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45794</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45188</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45637</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45460</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45189</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>44699</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45014</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>45631</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45702</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45702</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45841</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45695</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45259</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45841</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>45630</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45169</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45843</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45843</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45843</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45309</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>45734</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45791</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45747</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>45154</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>45302</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>45245</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>44974</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>44974</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>45215</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44985</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>45719</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28762,7 +28762,7 @@
         <v>45299</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>45721</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>45694</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45219</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>45320</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45198</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>44826</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45316</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
         <v>45148</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>45361</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>45975</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45213</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45734</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44988</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45980</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>45732</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45211</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44804</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44956</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44874</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>45277</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>45713</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45880</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>45880</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45259</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>45677</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>45732</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45880</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45009</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45881</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45881</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45264</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>45113</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>46098</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>45670</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>46098</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45169</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>45077</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>46101</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>46100</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>46101</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>46105</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45328</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>46105</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45083</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>46104</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>45488</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45069</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44904</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45279</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45700</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45481</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>46111</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>46108</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>44984</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>46113</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>45308</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>45693</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>46120</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45992</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45995</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>45995</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>44881</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>45754</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>45551</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>45999</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>46127</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45187</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>44902</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>46000</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>46129</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>44603</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44541</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45475</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>46135</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>46135</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45671</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45728</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>45402</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>46008</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>45184</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45091</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>45162</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>45887</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45412</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>46135</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>46135</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45343</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45889</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45270</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45595</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45604</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>46021</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>44916</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45733</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>46030</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45821</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44873</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>46001</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>45372</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45980</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>45069</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45277</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>46044</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>44976</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44980</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45694</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>46044</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>46048</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>45692</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>44484</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>46048</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
         <v>45916</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37056,7 +37056,7 @@
         <v>46140</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>46020</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>46049</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37275,7 +37275,7 @@
         <v>46051</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>46051</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>46055</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>46055</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>46055</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>46057</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>46059</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>46059</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>46061</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46146</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>46070</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>46071</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>46071</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>46074</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>46079</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>46029</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>46029</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>46154</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45742</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>46091</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>46091</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>46090</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>45838</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>46093</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>46093</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>46163</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>46170</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>46174</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>46174</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>46174</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>46174</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>46187</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>46187</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>46187</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>46190</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>46190</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>46196</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>46196</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>46196</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>46198</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>46198</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>46198</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>46202</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>46204</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>46209</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>46209</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>46209</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>46209</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40834,7 +40834,7 @@
         <v>46209</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>46209</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>46212</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>46197</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>46282</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>46283</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>46283</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>46243</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>46243</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>46283</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>46243</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
         <v>46243</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>46243</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>46283</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>46287</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>46290</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>46246</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>46289</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>46289</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>46000</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>46294</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>46294</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>46294</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>46294</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>46248</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>46295</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>46249</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>46295</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>46295</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>46295</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>46254</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>46258</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>46258</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>46260</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>46287</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>46283</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>46260</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45108</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45109</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>44613</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>44575</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45042</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45453</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45411</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45029</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45118</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45082</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45112</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44363,7 +44363,7 @@
         <v>44977</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>44482</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45103</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>45100</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45029</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45419</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45062</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45042</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45809</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45804</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45835</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>46091</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>46091</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>46209</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>46150</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>

--- a/Översikt NÄSSJÖ.xlsx
+++ b/Översikt NÄSSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46041</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45131</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46168</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45394</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45460</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45680</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45881</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>45919</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45517</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45804</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45692</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>46303</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45029</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>46258</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45393</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>45419</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45810</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>44537</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45096</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44819</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>45419</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44928</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45610</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>44848</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45527</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45943</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45645</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>45841</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45841</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44886</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>46104</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>46107</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>45590</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>45899</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>45841</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>46048</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>46049</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>46140</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>46283</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>46258</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45113</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45108</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>45013</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45051</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45712</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>44546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>44529</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>44503</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>44838</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>44588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44483</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>44827</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>44573</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>44691</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>44579</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>44603</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>44502</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>44818</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>44586</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>44508</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>44613</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>44844</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>44541</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>44837</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44670</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44519</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>44678</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>44750</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>44659</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>44701</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44524</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44579</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>44858</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>44887</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44811</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44650</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>44568</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>44487</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45363</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>45154</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>45021</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>44826</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>45188</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>45302</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>44816</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>45163</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>45757</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44874</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>45372</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>45372</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>45617</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>44848</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>45275</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>45732</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>44858</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44608</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>44858</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>44867</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45720</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>44928</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45370</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>45219</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>44902</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>45343</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>44928</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>44928</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44826</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44813</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45358</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45377</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>45203</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45412</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>45616</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45322</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>45182</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>45454</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>45380</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>45210</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>44564</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>44664</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>45394</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45460</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>45109</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>45732</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45391</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45391</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45303</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45013</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45610</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45380</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45460</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>45238</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45454</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45099</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45109</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>45567</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>44873</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>45614</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44487</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>45602</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45680</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45404</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>44665</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45617</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45365</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45266</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44992</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>44659</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>45517</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>45408</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>45307</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45008</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>45566</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>45046</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>45236</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45181</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45056</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44484</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>45277</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>45154</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45154</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>45742</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>45273</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>45704</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>45827</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>45800</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>45163</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>45841</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45679</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44946</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>45335</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>45335</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45238</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45890</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45485</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44993</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45257</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>44956</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45275</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45343</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44867</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45604</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45888</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45889</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45448</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45756</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45365</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>45899</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45644</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45625</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45734</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45246</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45106</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45328</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45328</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45238</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45904</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45904</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45873</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45907</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45907</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45373</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>44946</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45215</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45737</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45737</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45776</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45776</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45259</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45162</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45590</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45275</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45784</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45109</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45109</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45784</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45132</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>44609</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45166</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45148</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44994</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45615</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>45211</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45275</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45917</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45579</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45190</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45599</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44902</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>44605</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45446</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45742</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45014</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45503</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45118</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45320</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>45335</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45031</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45791</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45791</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45419</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44928</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45586</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45212</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45212</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45791</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45791</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45369</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45111</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45573</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45795</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>45795</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45372</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>44972</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44617</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45260</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45728</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45742</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45723</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45733</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45356</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45729</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45210</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45213</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>44945</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>44594</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45281</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45267</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>44988</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45693</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45181</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>44816</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45601</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45209</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>44972</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45162</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45372</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45372</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45372</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>44664</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>44894</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>45398</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45611</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45103</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>44945</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>45112</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45695</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>45168</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45943</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45943</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>44939</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45942</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>45944</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45317</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45041</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45818</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45009</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45685</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45013</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>45083</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45818</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45818</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44965</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>45702</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45824</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>45824</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45821</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45824</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>45824</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>45720</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45204</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>45951</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>44776</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>45187</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>45188</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45794</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45188</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45637</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45460</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45189</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>44699</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45014</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>45631</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45702</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45702</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45841</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45695</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45259</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45841</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>45630</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45169</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45843</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45843</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45843</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45309</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>45734</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45791</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45747</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>45154</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>45302</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>45245</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>44974</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>44974</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>45215</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44985</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>45719</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28762,7 +28762,7 @@
         <v>45299</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>45721</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>45694</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45219</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>45320</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45198</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>44826</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45316</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
         <v>45148</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>45361</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>45975</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45213</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45734</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44988</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45980</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>45732</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45211</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44804</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44956</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44874</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>45277</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>45713</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45880</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>45880</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45259</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>45677</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>45732</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45880</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45009</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45881</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45881</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45264</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>45113</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>46098</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>45670</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>46098</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45169</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>45077</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>46101</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>46100</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>46101</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>46105</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45328</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>46105</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45083</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>46104</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>45488</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45069</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44904</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45279</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45700</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45481</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>46111</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>46108</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>44984</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>46113</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>45308</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>45693</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>46120</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45992</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45995</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>45995</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>44881</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>45754</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>45551</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>45999</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>46127</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45187</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>44902</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>46000</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>46129</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>44603</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44541</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45475</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>46135</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>46135</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45671</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45728</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>45402</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>46008</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>45184</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45091</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>45162</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>45887</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45412</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>46135</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>46135</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45343</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45889</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45270</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45595</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45604</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>46021</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>44916</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45733</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>46030</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45821</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44873</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>46001</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>45372</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45980</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>45069</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45277</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>46044</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>44976</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44980</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45694</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>46044</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>46048</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>45692</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>44484</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>46048</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
         <v>45916</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37056,7 +37056,7 @@
         <v>46140</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>46020</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>46049</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37275,7 +37275,7 @@
         <v>46051</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>46051</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>46055</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>46055</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>46055</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>46057</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>46059</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>46059</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>46061</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46146</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>46070</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>46071</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>46071</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>46074</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>46079</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>46029</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>46029</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>46154</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45742</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>46091</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>46091</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>46090</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>45838</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>46093</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>46093</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>46163</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>46170</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>46174</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>46174</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>46174</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>46174</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>46187</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>46187</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>46187</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>46190</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>46190</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>46196</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>46196</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>46196</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>46198</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>46198</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>46198</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>46202</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>46204</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>46209</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>46209</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>46209</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>46209</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40834,7 +40834,7 @@
         <v>46209</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>46209</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>46212</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>46197</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>46282</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>46283</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>46283</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>46243</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>46243</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>46283</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>46243</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
         <v>46243</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>46243</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>46283</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>46287</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>46290</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>46246</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>46289</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>46289</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>46000</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>46294</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>46294</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>46294</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>46294</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>46248</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>46295</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>46249</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>46295</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>46295</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>46295</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>46254</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>46258</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>46258</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>46260</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>46287</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>46283</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>46260</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45108</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45109</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>44613</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>44575</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45042</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45453</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45411</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45029</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45118</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45082</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45112</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44363,7 +44363,7 @@
         <v>44977</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>44482</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45103</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>45100</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45029</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45419</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45062</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45042</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45809</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45804</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45835</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>46091</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>46091</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>46209</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>46150</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>

--- a/Översikt NÄSSJÖ.xlsx
+++ b/Översikt NÄSSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46041</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45131</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46168</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45460</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45394</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45919</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>45680</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45881</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45804</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>46303</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45692</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45029</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>45846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45393</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>45419</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45810</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>44537</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45590</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45419</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>44819</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>44928</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45527</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44928</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45096</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45841</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44586</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44848</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>45943</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>46140</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46049</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>46048</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>45610</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>46104</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>44886</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>45899</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>45530</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>46283</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>46258</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45841</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45841</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45108</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45113</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>45013</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45051</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45712</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>44546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>44529</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>44503</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>44838</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>44588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44827</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44573</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>44579</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>44603</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>44691</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>44818</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44508</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>44613</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44727</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>44844</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>44541</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>44519</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44659</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>44701</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44579</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>44670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44524</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>44487</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44678</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>44750</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44858</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44887</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44811</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>44650</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>44568</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>44635</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>45009</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>45481</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>45369</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>45454</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>44988</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45021</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>45213</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>45670</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>45754</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>45219</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>45704</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44972</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45238</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45154</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>45302</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45277</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>45031</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45166</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>45111</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>45162</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45380</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>45275</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45238</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44945</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44867</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>45637</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>45328</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45148</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45259</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>45109</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>45109</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>45335</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45335</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45485</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45189</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45188</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>45013</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45317</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45604</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45693</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45211</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45460</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45303</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45014</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45734</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45732</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45181</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>44928</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45475</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45182</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45412</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45677</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45188</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>45517</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45446</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45402</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45041</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44945</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>45154</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44699</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>45046</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>45212</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>45980</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>45827</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45488</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>45742</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>45841</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>45889</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>44928</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44928</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45732</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45821</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>44904</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44487</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45887</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>45322</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45800</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>45888</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>45679</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45889</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>45916</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45671</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45890</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>46001</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45211</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45245</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>45077</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>45899</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44939</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45733</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>46140</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>45343</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45694</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>44609</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45904</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45083</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>45573</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45904</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45873</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44946</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45460</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>44873</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>45907</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45907</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45737</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45737</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>45776</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45370</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44594</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45757</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45083</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45358</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45215</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>45365</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45365</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45917</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>44946</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>46146</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>45335</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>44956</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45631</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45106</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45412</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45601</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45162</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44980</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45361</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>44541</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45942</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45943</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45943</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44867</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44873</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45742</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>44776</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>45944</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45328</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45277</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>45742</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45448</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>45951</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>45398</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>44826</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44826</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>45702</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>46154</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45212</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>45363</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45008</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45391</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45391</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45838</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45299</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45118</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>44928</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45279</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45188</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45975</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>44804</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>46163</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45625</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45644</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45454</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45112</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45187</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>45980</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>44956</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44858</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45460</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45259</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45209</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45320</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45372</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45372</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45567</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45343</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45169</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45566</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45184</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45992</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45154</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45154</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45995</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45995</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45009</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45999</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>46000</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>46170</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44664</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45630</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45281</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>46174</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>45091</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45610</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>46174</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45694</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>46008</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>44974</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45720</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45210</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>46174</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44858</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>46174</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24120,7 +24120,7 @@
         <v>45270</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>46021</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>45203</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45680</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>46030</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45380</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45103</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45604</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45257</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>45302</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45069</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>46044</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>46044</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>46048</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>46048</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>45693</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>46049</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45168</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>46051</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>46055</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>46051</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>46055</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>46055</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>46057</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>46059</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>46059</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>46061</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45404</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45215</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>45259</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>46070</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>46187</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>46187</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>46071</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>46071</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>46074</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>46029</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45069</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>46079</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>46029</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>46187</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45266</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44874</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45614</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>46090</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45246</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>46190</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>46190</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>46091</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>46091</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>45148</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>46093</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>46093</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>46098</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>46196</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>46098</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>44664</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45210</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>46100</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>46104</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>44902</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>46101</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>46101</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>45198</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>46196</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45590</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>46196</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>46105</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45595</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>46105</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>46108</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>46198</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>46111</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>46198</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45236</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>46198</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29698,7 +29698,7 @@
         <v>45419</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>45756</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>46113</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>44813</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>46120</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30068,7 +30068,7 @@
         <v>44816</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30141,7 +30141,7 @@
         <v>45169</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>46127</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>46202</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>46129</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>45734</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>45372</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>45372</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>45372</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>45132</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>44816</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>46135</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>46135</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>44972</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45728</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31163,7 +31163,7 @@
         <v>44994</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45373</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>46135</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>46135</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>46204</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>46020</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         <v>45394</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44993</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45692</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>45219</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45695</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>46209</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45617</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>46209</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>46209</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>46209</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>46209</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>46209</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44564</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>44985</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45372</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45372</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45617</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45190</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>46212</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44617</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>45163</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44974</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>45109</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>45014</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>44988</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>44894</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45695</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45408</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>45162</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44826</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>46197</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>44608</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33967,7 +33967,7 @@
         <v>44976</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>45213</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>45343</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>44881</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45377</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>44659</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45264</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45700</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>44916</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>46282</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>44984</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45579</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>45187</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>45308</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>44992</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>46283</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45238</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>46287</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>45275</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45181</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>46243</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>46283</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>46283</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45732</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>46243</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>46243</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>45275</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>46243</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>46243</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>46283</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45099</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>45056</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>46246</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45616</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>44665</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>44848</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45309</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>45113</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>44874</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45273</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>45204</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>46000</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>46289</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>46289</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45734</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46290</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45163</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>44603</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45307</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45316</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>46249</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44902</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>44902</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>46294</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>46295</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45013</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>46294</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>46294</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45109</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>45602</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45685</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>46248</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>46295</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>46295</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>46294</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>46295</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>45702</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>45702</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45328</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>44965</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45551</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>46254</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45275</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45277</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45611</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45776</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>46258</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>46258</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45615</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45784</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45784</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>45599</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>46260</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>44605</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>46260</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>45320</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>45586</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45791</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45791</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45791</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>45791</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>46283</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45795</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>45260</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45795</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45728</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45742</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>45356</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45733</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>46307</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45723</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>45729</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45267</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>46309</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45818</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45818</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>45818</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45824</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45821</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>45824</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45824</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45824</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>46287</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>45794</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>45841</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>45841</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45843</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>45843</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>45843</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45747</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45791</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45719</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>45721</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>45732</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>45713</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45881</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45880</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>45881</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45880</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45880</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45109</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45108</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45042</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45453</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45411</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45029</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45118</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43993,7 +43993,7 @@
         <v>45082</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>45112</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>44977</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45103</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45100</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45029</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>44613</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45419</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>44575</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45062</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45042</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45809</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45804</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>45835</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>46091</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>46091</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>46209</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>46150</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>

--- a/Översikt NÄSSJÖ.xlsx
+++ b/Översikt NÄSSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46041</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45131</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46168</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45460</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45394</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45919</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>45680</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45881</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45804</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>46303</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45692</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45029</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>45846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45393</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>45419</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45810</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>44537</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45590</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45419</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>44819</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>44928</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45527</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44928</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45096</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45841</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44586</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44848</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>45943</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>46140</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46049</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>46048</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>45610</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>46104</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>44886</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>45899</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>45530</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>46283</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>46258</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45841</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45841</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45108</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45113</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>45013</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45051</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45712</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>44546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>44529</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>44503</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>44838</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>44588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44827</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44573</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>44579</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>44603</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>44691</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>44818</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44508</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>44613</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44727</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>44844</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>44541</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>44519</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44659</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>44701</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44579</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>44670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44524</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>44487</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44678</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>44750</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44858</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44887</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44811</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>44650</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>44568</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>44635</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>45009</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>45481</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>45369</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>45454</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>44988</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45021</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>45213</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>45670</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>45754</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>45219</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>45704</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44972</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45238</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45154</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>45302</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45277</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>45031</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45166</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>45111</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>45162</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45380</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>45275</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45238</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44945</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44867</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>45637</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>45328</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45148</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45259</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>45109</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>45109</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>45335</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45335</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45485</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45189</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45188</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>45013</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45317</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45604</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45693</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45211</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45460</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45303</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45014</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45734</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45732</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45181</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>44928</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45475</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45182</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45412</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45677</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45188</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>45517</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45446</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45402</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45041</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44945</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>45154</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44699</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>45046</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>45212</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>45980</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>45827</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45488</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>45742</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>45841</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>45889</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>44928</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44928</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45732</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45821</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>44904</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44487</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45887</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>45322</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45800</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>45888</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>45679</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45889</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>45916</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45671</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45890</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>46001</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45211</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45245</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>45077</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>45899</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44939</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45733</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>46140</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>45343</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45694</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>44609</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45904</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45083</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>45573</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45904</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45873</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44946</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45460</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>44873</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>45907</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45907</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45737</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45737</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>45776</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45370</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44594</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45757</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45083</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45358</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45215</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>45365</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45365</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45917</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>44946</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>46146</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>45335</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>44956</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45631</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45106</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45412</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45601</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45162</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44980</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45361</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>44541</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45942</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45943</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45943</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44867</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44873</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45742</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>44776</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>45944</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45328</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45277</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>45742</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45448</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>45951</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>45398</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>44826</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44826</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>45702</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>46154</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45212</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>45363</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45008</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45391</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45391</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45838</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45299</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45118</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>44928</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45279</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45188</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45975</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>44804</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>46163</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45625</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45644</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45454</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45112</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45187</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>45980</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>44956</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44858</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45460</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45259</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45209</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45320</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45372</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45372</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45567</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45343</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45169</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45566</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45184</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45992</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45154</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45154</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45995</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45995</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45009</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45999</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>46000</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>46170</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44664</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45630</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45281</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>46174</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>45091</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45610</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>46174</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45694</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>46008</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>44974</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45720</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45210</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>46174</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44858</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>46174</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24120,7 +24120,7 @@
         <v>45270</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>46021</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>45203</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45680</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>46030</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45380</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45103</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45604</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45257</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>45302</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45069</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>46044</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>46044</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>46048</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>46048</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>45693</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>46049</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45168</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>46051</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>46055</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>46051</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>46055</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>46055</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>46057</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>46059</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>46059</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>46061</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45404</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45215</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>45259</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>46070</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>46187</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>46187</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>46071</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>46071</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>46074</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>46029</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45069</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>46079</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>46029</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>46187</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45266</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44874</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45614</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>46090</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45246</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>46190</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>46190</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>46091</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>46091</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>45148</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>46093</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>46093</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>46098</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>46196</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>46098</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>44664</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45210</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>46100</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>46104</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>44902</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>46101</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>46101</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>45198</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>46196</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45590</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>46196</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>46105</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45595</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>46105</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>46108</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>46198</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>46111</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>46198</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45236</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>46198</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29698,7 +29698,7 @@
         <v>45419</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>45756</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>46113</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>44813</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>46120</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30068,7 +30068,7 @@
         <v>44816</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30141,7 +30141,7 @@
         <v>45169</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>46127</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>46202</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>46129</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>45734</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>45372</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>45372</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>45372</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>45132</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>44816</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>46135</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>46135</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>44972</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45728</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31163,7 +31163,7 @@
         <v>44994</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45373</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>46135</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>46135</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>46204</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>46020</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         <v>45394</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44993</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45692</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>45219</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45695</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>46209</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45617</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>46209</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>46209</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>46209</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>46209</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>46209</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44564</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>44985</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45372</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45372</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45617</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45190</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>46212</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44617</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>45163</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44974</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>45109</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>45014</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>44988</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>44894</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45695</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45408</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>45162</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44826</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>46197</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>44608</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33967,7 +33967,7 @@
         <v>44976</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>45213</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>45343</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>44881</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45377</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>44659</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45264</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45700</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>44916</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>46282</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>44984</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45579</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>45187</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>45308</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>44992</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>46283</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45238</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>46287</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>45275</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45181</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>46243</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>46283</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>46283</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45732</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>46243</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>46243</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>45275</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>46243</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>46243</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>46283</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45099</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>45056</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>46246</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45616</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>44665</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>44848</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45309</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>45113</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>44874</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45273</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>45204</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>46000</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>46289</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>46289</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45734</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46290</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45163</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>44603</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45307</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45316</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>46249</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44902</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>44902</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>46294</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>46295</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45013</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>46294</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>46294</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45109</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>45602</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45685</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>46248</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>46295</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>46295</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>46294</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>46295</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>45702</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>45702</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45328</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>44965</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45551</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>46254</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45275</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45277</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45611</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45776</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>46258</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>46258</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45615</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45784</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45784</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>45599</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>46260</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>44605</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>46260</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>45320</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>45586</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45791</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45791</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45791</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>45791</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>46283</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45795</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>45260</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45795</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45728</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45742</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>45356</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45733</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>46307</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45723</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>45729</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45267</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>46309</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45818</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45818</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>45818</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45824</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45821</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>45824</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45824</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45824</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>46287</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>45794</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>45841</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>45841</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45843</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>45843</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>45843</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45747</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45791</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45719</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>45721</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>45732</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>45713</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45881</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45880</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>45881</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45880</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45880</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45109</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45108</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45042</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45453</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45411</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45029</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45118</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43993,7 +43993,7 @@
         <v>45082</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>45112</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>44977</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45103</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45100</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45029</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>44613</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45419</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>44575</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45062</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45042</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45809</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45804</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>45835</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>46091</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>46091</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>46209</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>46150</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>

--- a/Översikt NÄSSJÖ.xlsx
+++ b/Översikt NÄSSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46041</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45131</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46168</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45394</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45517</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>45919</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45881</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>45460</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45680</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45804</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45692</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>46303</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45029</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>46258</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45393</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>45419</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45810</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>44537</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45590</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44928</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>45943</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45610</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>46021</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>46283</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45419</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>46048</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>46049</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45841</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45841</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>46104</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>44928</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>46107</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46258</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>44848</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>45899</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>45841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45527</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>46140</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>45645</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>45530</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45096</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>44586</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44819</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44886</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45113</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45108</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>45013</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45051</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45712</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>44546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>44529</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>44503</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>44838</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>44588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44827</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44573</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>44691</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>44579</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>44603</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>44818</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44508</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>44613</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44727</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>44844</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>44541</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>44519</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44659</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>44701</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44579</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>44670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44524</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>44678</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44750</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>44858</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44887</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44635</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44811</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>44650</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>44568</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>44541</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>45475</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>45742</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>45827</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>44816</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>45800</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45617</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>45720</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>45841</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>45679</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45219</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>45343</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>44826</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44813</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45358</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45377</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>45890</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45203</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>45402</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45322</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>45888</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>45889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45184</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>45091</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45162</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45412</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>45567</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45343</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>45404</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>45899</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45363</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45270</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45595</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>45904</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45604</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>45873</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44916</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>45907</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>45907</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45838</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>45737</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45737</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45776</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44873</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>46163</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>45372</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45917</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>45069</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45277</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44976</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44980</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>44874</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>46170</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>46174</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>46174</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>44848</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>44858</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>44867</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45154</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>46174</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>44928</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45021</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>45943</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45943</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45188</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>46174</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45302</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45942</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45210</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45394</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>45460</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>45372</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>45372</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45454</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45109</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>45944</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45370</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44902</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>45412</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>45616</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45182</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>45951</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45454</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>44564</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>45303</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>46187</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>46187</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>46187</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45460</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45238</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>45099</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>44873</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45614</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>45602</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>45680</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>46190</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>46190</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45617</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>44659</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>46196</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>46196</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>46196</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>45008</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>45566</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>46198</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45046</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>45236</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>45975</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45181</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>46198</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>46198</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45980</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>46202</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>45365</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45056</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45266</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45704</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>46204</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45238</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>45257</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45343</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>45448</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>46209</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>46209</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>46209</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>46209</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45756</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>46209</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>46209</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45365</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45644</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45625</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45734</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>45517</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>45307</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45992</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>46212</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45995</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45328</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>45328</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45238</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45995</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45999</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>45215</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>46000</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45776</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>46197</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>45784</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45784</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>46008</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>45615</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45599</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>44605</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>46021</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>46282</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>46030</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>45320</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>46283</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>45791</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>45791</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>46283</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45586</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>46243</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>45791</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45791</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>46243</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45795</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>46283</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>46243</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>46243</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>46243</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>45795</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>46283</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45260</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45728</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45154</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45154</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>46044</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45742</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45723</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45733</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>46044</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45356</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>46048</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45729</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>46048</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>46287</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45267</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>46049</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>46290</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46246</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>46051</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>46051</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>46289</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>46055</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45273</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>46055</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46000</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>46055</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>46057</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>46059</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>46059</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>46061</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>46294</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45818</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>46294</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>46294</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>46070</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45818</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>45818</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44946</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>46294</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>46248</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>46071</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>46071</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>45824</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24958,7 +24958,7 @@
         <v>45824</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>46074</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45821</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45824</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45824</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>46295</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>46249</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>46079</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>46295</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>46295</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>46295</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>46029</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>46029</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45794</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>46091</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>46091</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>46090</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>46093</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>46093</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45485</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>46098</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44867</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45841</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>45841</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>46254</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>45604</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>45843</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45843</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>46101</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>46100</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>46101</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45843</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>46105</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46105</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45791</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45747</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>46104</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>46258</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>46258</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>46111</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>46108</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45719</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>45721</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>46113</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45246</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>46260</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>46120</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45732</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>46283</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>46260</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>46127</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>46307</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45713</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45880</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>45880</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>46129</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45880</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45881</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45881</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>46135</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>46135</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45671</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45728</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45887</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>46135</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>46135</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>44994</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>46309</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45889</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45733</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45821</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>44902</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>46289</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>46314</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>46001</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>45014</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45031</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>45980</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45419</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>44928</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45212</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45212</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45369</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>46315</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45694</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45573</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45372</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>44972</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45692</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45916</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>44617</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>46140</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>46020</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>46098</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>46317</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45213</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>44945</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45693</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45181</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45209</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>46287</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>46146</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>44972</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44894</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45398</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>44945</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45112</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>44939</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>46154</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45317</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>45742</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45041</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45009</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45013</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>44965</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>45204</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>45637</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>45014</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>45631</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45702</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45702</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45630</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>45154</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>44974</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44974</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>44985</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45694</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45198</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>44826</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45148</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44988</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>44804</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45277</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45677</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45732</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45670</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45169</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45077</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>45083</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45069</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>45700</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>45481</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44826</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>45163</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>45757</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>45275</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>45732</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44608</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>44858</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44928</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>44928</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>45380</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44664</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45109</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>45732</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>45391</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45391</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>45013</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45610</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>45380</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>44665</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>44992</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>45408</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45277</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>45163</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>45335</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45335</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44993</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>44956</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45275</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45106</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45373</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>44946</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45259</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>45162</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>45590</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>45275</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>45109</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>45109</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45132</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>44609</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>45166</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45148</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>45211</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45275</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45579</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45190</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>45446</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45742</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45503</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45118</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45335</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45111</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>45210</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44594</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45281</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>44988</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>44816</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45601</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>45162</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45372</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45372</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45372</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>44664</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>45611</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45103</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45695</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>45168</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>45685</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>45083</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>45702</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>45720</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>44776</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>45187</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>45188</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45188</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>45460</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45189</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>44699</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>45695</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>45259</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>45169</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>45309</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45734</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>45302</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>45245</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45215</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>45299</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45219</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>45320</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>45316</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45361</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>45213</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45734</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45211</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>44956</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>44874</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>45259</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>45009</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45264</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>45113</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>45328</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45488</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>44904</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45279</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>44984</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>45308</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>45693</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>44881</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45754</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>45551</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45187</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>44902</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>44603</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45108</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45109</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>44613</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>44575</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45042</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45453</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43993,7 +43993,7 @@
         <v>45411</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>45029</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>45118</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45082</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45112</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>44977</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45103</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45100</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45029</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45419</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45062</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45042</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45809</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>45804</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45835</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>46091</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>46091</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>46209</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>46150</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>

--- a/Översikt NÄSSJÖ.xlsx
+++ b/Översikt NÄSSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46041</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45131</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46168</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45394</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45517</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>45919</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45881</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>45460</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45680</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45411</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45804</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45692</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>46303</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45029</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>46258</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45393</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>45419</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45810</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>44537</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45590</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44928</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>45943</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45610</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>46021</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>46283</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45419</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>46048</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>46049</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45841</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45841</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>46104</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>44928</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>46107</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46258</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>44848</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>45899</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>45841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45527</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>46140</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>45645</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>45530</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45096</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>44586</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44819</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44886</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45113</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45108</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>45013</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45051</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45712</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>44546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>44529</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>44503</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>44838</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>44588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44827</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44573</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>44691</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>44579</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>44603</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>44818</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44508</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>44613</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44727</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>44844</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>44541</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>44519</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44659</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>44701</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44579</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>44670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44524</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>44678</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44750</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>44858</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44887</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44635</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44811</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>44650</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>44568</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>44541</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>45475</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>45742</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>45827</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>44816</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>45800</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45617</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>45720</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>45841</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>45679</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45219</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>45343</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>44826</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44813</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45358</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45377</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>45890</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45203</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>45402</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45322</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>45888</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>45889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45184</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>45091</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45162</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45412</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>45567</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45343</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>45404</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>45899</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45363</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45270</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45595</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>45904</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45604</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>45873</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44916</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>45907</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>45907</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45838</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>45737</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45737</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45776</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44873</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>46163</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>45372</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45917</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>45069</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45277</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44976</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44980</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>44874</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>46170</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>46174</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>46174</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>44848</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>44858</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>44867</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45154</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>46174</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>44928</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45021</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>45943</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45943</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45188</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>46174</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45302</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45942</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45210</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45394</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>45460</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>45372</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>45372</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45454</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45109</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>45944</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45370</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44902</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>45412</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>45616</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45182</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>45951</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45454</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>44564</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>45303</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>46187</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>46187</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>46187</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45460</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45238</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>45099</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>44873</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45614</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>45602</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>45680</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>46190</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>46190</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45617</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>44659</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>46196</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>46196</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>46196</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>45008</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>45566</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>46198</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45046</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>45236</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>45975</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45181</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>46198</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>46198</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45980</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>46202</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>45365</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45056</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45266</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45704</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>46204</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45238</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>45257</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45343</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>45448</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>46209</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>46209</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>46209</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>46209</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45756</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>46209</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>46209</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45365</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45644</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45625</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45734</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>45517</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>45307</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45992</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>46212</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45995</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45328</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>45328</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45238</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45995</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45999</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>45215</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>46000</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45776</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>46197</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>45784</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45784</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>46008</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>45615</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45599</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>44605</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>46021</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>46282</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>46030</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>45320</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>46283</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>45791</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>45791</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>46283</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45586</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>46243</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>45791</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45791</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>46243</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45795</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>46283</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>46243</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>46243</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>46243</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>45795</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>46283</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45260</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45728</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45154</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45154</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>46044</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45742</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45723</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45733</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>46044</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45356</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>46048</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45729</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>46048</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>46287</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45267</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>46049</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>46290</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46246</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>46051</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>46051</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>46289</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>46055</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45273</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>46055</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46000</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>46055</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>46057</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>46059</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>46059</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>46061</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>46294</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45818</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>46294</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>46294</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>46070</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45818</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>45818</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44946</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>46294</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>46248</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>46071</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>46071</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>45824</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24958,7 +24958,7 @@
         <v>45824</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>46074</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45821</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45824</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45824</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>46295</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>46249</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>46079</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>46295</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>46295</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>46295</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>46029</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>46029</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45794</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>46091</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>46091</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>46090</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>46093</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>46093</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45485</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>46098</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44867</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45841</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>45841</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>46254</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>45604</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>45843</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45843</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>46101</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>46100</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>46101</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45843</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>46105</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46105</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45791</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45747</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>46104</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>46258</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>46258</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>46111</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>46108</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45719</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>45721</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>46113</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45246</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>46260</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>46120</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45732</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>46283</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>46260</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>46127</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>46307</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45713</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45880</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>45880</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>46129</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45880</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45881</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45881</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>46135</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>46135</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45671</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45728</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45887</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>46135</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>46135</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>44994</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>46309</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45889</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45733</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45821</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>44902</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>46289</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>46314</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>46001</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>45014</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45031</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>45980</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45419</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>44928</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45212</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45212</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45369</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>46315</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45694</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45573</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45372</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>44972</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45692</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45916</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>44617</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>46140</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>46020</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>46098</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>46317</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45213</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>44945</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45693</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45181</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45209</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>46287</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>46146</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>44972</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44894</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45398</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>44945</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45112</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>44939</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>46154</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45317</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>45742</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45041</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45009</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45013</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>44965</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>45204</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>45637</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>45014</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>45631</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45702</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45702</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45630</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>45154</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>44974</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44974</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>44985</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45694</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45198</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>44826</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45148</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44988</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>44804</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45277</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45677</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45732</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45670</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45169</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45077</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>45083</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45069</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>45700</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>45481</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44826</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>45163</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>45757</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>45275</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>45732</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44608</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>44858</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44928</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>44928</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>45380</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44664</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45109</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>45732</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>45391</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45391</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>45013</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45610</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>45380</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>44665</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>44992</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>45408</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45277</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>45163</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>45335</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45335</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44993</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>44956</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45275</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45106</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45373</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>44946</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45259</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>45162</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>45590</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>45275</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>45109</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>45109</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45132</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>44609</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>45166</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45148</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>45211</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45275</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45579</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45190</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>45446</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45742</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45503</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45118</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45335</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45111</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>45210</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44594</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45281</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>44988</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>44816</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45601</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>45162</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45372</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45372</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45372</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>44664</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>45611</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45103</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45695</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>45168</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>45685</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>45083</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>45702</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>45720</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>44776</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>45187</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>45188</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45188</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>45460</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45189</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>44699</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>45695</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>45259</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>45169</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>45309</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45734</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>45302</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>45245</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45215</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>45299</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45219</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>45320</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>45316</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45361</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>45213</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45734</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45211</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>44956</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>44874</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>45259</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>45009</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45264</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>45113</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>45328</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45488</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>44904</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45279</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>44984</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>45308</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>45693</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>44881</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45754</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>45551</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45187</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>44902</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>44603</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45108</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45109</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>44613</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>44575</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45042</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45453</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43993,7 +43993,7 @@
         <v>45411</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>45029</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>45118</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45082</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45112</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>44977</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45103</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45100</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45029</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45419</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45062</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45042</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45809</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>45804</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45835</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>46091</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>46091</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>46209</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>46150</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
